--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-15T19:11:07+00:00</t>
+    <t>2026-01-16T14:21:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-16T14:21:16+00:00</t>
+    <t>2026-01-19T10:22:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T10:22:08+00:00</t>
+    <t>2026-01-20T10:13:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T10:13:19+00:00</t>
+    <t>2026-01-21T17:03:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T17:03:29+00:00</t>
+    <t>2026-01-22T09:24:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-22T09:24:15+00:00</t>
+    <t>2026-01-22T12:59:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-22T12:59:21+00:00</t>
+    <t>2026-01-22T14:02:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-22T14:02:02+00:00</t>
+    <t>2026-01-23T19:34:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-23T19:34:42+00:00</t>
+    <t>2026-01-26T15:48:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T15:48:48+00:00</t>
+    <t>2026-01-28T08:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -9,6 +9,9 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$29</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T08:09:20+00:00</t>
+    <t>2026-01-28T19:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Arzneimittel</t>
+    <t>Bildet ein Arzneimittel ab, das nicht über eine PZN verfügt (z.B. magistrale Zubereitungen).</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -475,7 +478,7 @@
 </t>
   </si>
   <si>
-    <t>Business identifier for this medication</t>
+    <t>Eindeutiger Identifikator für das Arzneimittel. Verwendung für magistrale Zubereitungen prüfen.</t>
   </si>
   <si>
     <t>Business identifier for this medication.</t>
@@ -497,7 +500,7 @@
 </t>
   </si>
   <si>
-    <t>Codes that identify this medication</t>
+    <t>Code des Arzneimittels. Verwendung für magistrale Zubereitungen prüfen.</t>
   </si>
   <si>
     <t>A code (or set of codes) that specify this medication, or a textual description if no code is available. Usage note: This could be a standard medication code such as a code from RxNorm, SNOMED CT, IDMP etc. It could also be a national or local formulary code, optionally with translations to other code systems.</t>
@@ -534,7 +537,7 @@
     <t>Medication.status</t>
   </si>
   <si>
-    <t>active | inactive | entered-in-error</t>
+    <t>Der Verfügbarkeitsstatus active | inactive | entered-in-error. Verwendung für magistrale Zubereitungen prüfen</t>
   </si>
   <si>
     <t>A code to indicate if the medication is in active use.</t>
@@ -558,11 +561,11 @@
     <t>Medication.manufacturer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-organization)
 </t>
   </si>
   <si>
-    <t>Manufacturer of the item</t>
+    <t>Der Hersteller des Arzneimittels. Für magistrale Zubereitungen die Apotheke. 1..1 ?</t>
   </si>
   <si>
     <t>Describes the details of the manufacturer of the medication product.  This is not intended to represent the distributor of a medication product.</t>
@@ -583,7 +586,7 @@
     <t>Medication.form</t>
   </si>
   <si>
-    <t>powder | tablets | capsule +</t>
+    <t>Die Darreichungsform des Arzneimittels</t>
   </si>
   <si>
     <t>Describes the form of the item.  Powder; tablets; capsule.</t>
@@ -616,7 +619,7 @@
 </t>
   </si>
   <si>
-    <t>Amount of drug in package</t>
+    <t>Die Gesamtmenge des Arzneimittels in der Verpackung.</t>
   </si>
   <si>
     <t>Specific amount of the drug in the packaged product.  For example, when specifying a product that has the same strength (For example, Insulin glargine 100 unit per mL solution for injection), this attribute provides additional clarification of the package amount (For example, 3 mL, 10mL, etc.).</t>
@@ -692,8 +695,8 @@
     <t>Medication.ingredient.item[x]</t>
   </si>
   <si>
-    <t>CodeableConcept
-Reference(Substance|4.0.1|Medication|4.0.1)</t>
+    <t xml:space="preserve">Reference(Substance|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-medication)
+</t>
   </si>
   <si>
     <t>The actual ingredient or content</t>
@@ -749,7 +752,7 @@
     <t>Medication.batch</t>
   </si>
   <si>
-    <t>Details about packaged medications</t>
+    <t>Informationen zur Charge des Arzneimittels. Verwendung für magistrale Zubereitungen prüfen.</t>
   </si>
   <si>
     <t>Information that only applies to packages (not products).</t>
@@ -924,6 +927,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1118,7 +1136,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="36.54296875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="75.19140625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1271,7 +1289,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -1383,7 +1401,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>86</v>
       </c>
@@ -1497,7 +1515,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>94</v>
       </c>
@@ -1609,7 +1627,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>100</v>
       </c>
@@ -1723,7 +1741,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>106</v>
       </c>
@@ -1837,7 +1855,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>115</v>
       </c>
@@ -1951,7 +1969,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>123</v>
       </c>
@@ -2065,7 +2083,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>131</v>
       </c>
@@ -2179,7 +2197,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>139</v>
       </c>
@@ -2295,7 +2313,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>144</v>
       </c>
@@ -2409,7 +2427,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>151</v>
       </c>
@@ -2523,7 +2541,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>163</v>
       </c>
@@ -2656,7 +2674,7 @@
         <v>87</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>21</v>
@@ -2762,13 +2780,13 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>21</v>
@@ -2863,7 +2881,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>188</v>
       </c>
@@ -2975,7 +2993,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>193</v>
       </c>
@@ -3089,7 +3107,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>199</v>
       </c>
@@ -3201,7 +3219,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>205</v>
       </c>
@@ -3315,7 +3333,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>208</v>
       </c>
@@ -3431,7 +3449,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>213</v>
       </c>
@@ -3545,7 +3563,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>220</v>
       </c>
@@ -3659,7 +3677,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>226</v>
       </c>
@@ -3771,7 +3789,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>231</v>
       </c>
@@ -3883,7 +3901,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>235</v>
       </c>
@@ -3995,7 +4013,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>236</v>
       </c>
@@ -4109,7 +4127,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>237</v>
       </c>
@@ -4225,7 +4243,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>238</v>
       </c>
@@ -4337,7 +4355,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
         <v>242</v>
       </c>
@@ -4450,6 +4468,24 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AN29">
+    <filterColumn colId="7">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="27">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI28">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T19:29:09+00:00</t>
+    <t>2026-01-29T08:16:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>ELGA e-Medikation Medication</t>
+    <t>ELGA e-Med Medikation</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T08:16:48+00:00</t>
+    <t>2026-01-29T15:27:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Bildet ein Arzneimittel ab, das nicht über eine PZN verfügt (z.B. magistrale Zubereitungen).</t>
+    <t>**Beschreibung:** Bildet ein Arzneimittel ab, das nicht über eine PZN verfügt, z.B. magistrale Zubereitungen ("Medication"-Ressource).</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -695,8 +695,8 @@
     <t>Medication.ingredient.item[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Substance|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-medication)
-</t>
+    <t>CodeableConcept
+Reference(Substance|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-medication)</t>
   </si>
   <si>
     <t>The actual ingredient or content</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T15:27:43+00:00</t>
+    <t>2026-01-30T14:55:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T14:55:57+00:00</t>
+    <t>2026-02-09T17:27:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$31</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="257">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T17:27:03+00:00</t>
+    <t>2026-02-10T17:53:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,8 @@
     <t>Description</t>
   </si>
   <si>
-    <t>**Beschreibung:** Bildet ein Arzneimittel ab, das nicht über eine PZN verfügt, z.B. magistrale Zubereitungen ("Medication"-Ressource).</t>
+    <t>**Beschreibung:** Bildet ein Arzneimittel ab, das nicht über eine PZN verfügt, z.B. magistrale Zubereitungen ("Medication"-Ressource).
+Wird die Ressource nur für magistrale Zubreitungen verwendet? Wirkstoffverschreibung? manufacturer immer ATAPSOrganization?</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -537,7 +538,7 @@
     <t>Medication.status</t>
   </si>
   <si>
-    <t>Der Verfügbarkeitsstatus active | inactive | entered-in-error. Verwendung für magistrale Zubereitungen prüfen</t>
+    <t>Verfügbarkeitsstatus des Arzneimittels:(req) active | inactive | entered-in-error. Verwendung für magistrale Zubereitungen prüfen</t>
   </si>
   <si>
     <t>A code to indicate if the medication is in active use.</t>
@@ -565,7 +566,7 @@
 </t>
   </si>
   <si>
-    <t>Der Hersteller des Arzneimittels. Für magistrale Zubereitungen die Apotheke. 1..1 ?</t>
+    <t>Der Hersteller des Arzneimittels. Für magistrale Zubereitungen die Apotheke (1..1?)</t>
   </si>
   <si>
     <t>Describes the details of the manufacturer of the medication product.  This is not intended to represent the distributor of a medication product.</t>
@@ -586,7 +587,7 @@
     <t>Medication.form</t>
   </si>
   <si>
-    <t>Die Darreichungsform des Arzneimittels</t>
+    <t>Die Darreichungsform des Arzneimittels: (ex) powder | tablets | capsule + https://hl7.org/fhir/R4/valueset-medication-form-codes.html</t>
   </si>
   <si>
     <t>Describes the form of the item.  Powder; tablets; capsule.</t>
@@ -708,10 +709,39 @@
     <t>The ingredient may reference a substance (for example, amoxicillin) or another medication (for example in the case of a compounded product, Glaxal Base).</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t>.player</t>
   </si>
   <si>
     <t>RXC-2-Component Code  if medication: RXO-1-Requested Give Code / RXE-2-Give Code / RXD-2-Dispense/Give Code / RXG-4-Give Code / RXA-5-Administered Code</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept</t>
+  </si>
+  <si>
+    <t>itemCodeableConcept</t>
+  </si>
+  <si>
+    <t>Inhaltsstoff codiert</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemReference</t>
+  </si>
+  <si>
+    <t>itemReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Substance|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-medication)
+</t>
+  </si>
+  <si>
+    <t>Referenz auf Ressourcen Substance oder Medication</t>
   </si>
   <si>
     <t>Medication.ingredient.isActive</t>
@@ -721,7 +751,7 @@
 </t>
   </si>
   <si>
-    <t>Active ingredient indicator</t>
+    <t>Aktive Wirkstoff TRUE/FALSE</t>
   </si>
   <si>
     <t>Indication of whether this ingredient affects the therapeutic action of the drug.</t>
@@ -737,7 +767,7 @@
     <t>Medication.ingredient.strength</t>
   </si>
   <si>
-    <t>Quantity of ingredient present</t>
+    <t>Menge der vorhandenen Zutat</t>
   </si>
   <si>
     <t>Specifies how many (or how much) of the items there are in this Medication.  For example, 250 mg per tablet.  This is expressed as a ratio where the numerator is 250mg and the denominator is 1 tablet.</t>
@@ -773,7 +803,7 @@
     <t>Medication.batch.lotNumber</t>
   </si>
   <si>
-    <t>Identifier assigned to batch</t>
+    <t>Identifkation der Charge</t>
   </si>
   <si>
     <t>The assigned lot number of a batch of the specified product.</t>
@@ -789,7 +819,7 @@
 </t>
   </si>
   <si>
-    <t>When batch will expire</t>
+    <t>Ablaufdatum</t>
   </si>
   <si>
     <t>When this specific batch of product will expire.</t>
@@ -1123,12 +1153,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN29"/>
+  <dimension ref="A1:AN31"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="32.79296875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="42.22265625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="32.79296875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="18.3359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -2881,7 +2911,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>188</v>
       </c>
@@ -2900,7 +2930,7 @@
         <v>87</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>21</v>
@@ -2993,7 +3023,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>193</v>
       </c>
@@ -3006,13 +3036,13 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>21</v>
@@ -3524,16 +3554,14 @@
         <v>21</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="AC21" s="2"/>
       <c r="AD21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>21</v>
+        <v>219</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>213</v>
@@ -3554,23 +3582,25 @@
         <v>159</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="22" hidden="true">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="D22" t="s" s="2">
         <v>21</v>
       </c>
@@ -3582,7 +3612,7 @@
         <v>87</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>21</v>
@@ -3591,17 +3621,17 @@
         <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>221</v>
+        <v>152</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -3650,10 +3680,10 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>87</v>
@@ -3665,26 +3695,28 @@
         <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="AM22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" hidden="true">
-      <c r="A23" t="s" s="2">
+      <c r="B23" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="C23" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="B23" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>21</v>
       </c>
@@ -3696,7 +3728,7 @@
         <v>87</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>21</v>
@@ -3705,16 +3737,18 @@
         <v>21</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>189</v>
+        <v>227</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+      <c r="O23" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>21</v>
       </c>
@@ -3762,10 +3796,10 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>87</v>
@@ -3777,24 +3811,24 @@
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="24" hidden="true">
-      <c r="A24" t="s" s="2">
-        <v>231</v>
-      </c>
       <c r="B24" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3808,7 +3842,7 @@
         <v>87</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>21</v>
@@ -3817,16 +3851,18 @@
         <v>21</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>194</v>
+        <v>230</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" s="2"/>
+      <c r="O24" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>21</v>
       </c>
@@ -3874,7 +3910,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -3889,7 +3925,7 @@
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>234</v>
@@ -3901,7 +3937,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>235</v>
       </c>
@@ -3920,7 +3956,7 @@
         <v>87</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>21</v>
@@ -3929,13 +3965,13 @@
         <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>201</v>
+        <v>236</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>202</v>
+        <v>237</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3986,7 +4022,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -3998,41 +4034,41 @@
         <v>21</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>21</v>
+        <v>238</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" hidden="true">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>21</v>
@@ -4041,17 +4077,15 @@
         <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>133</v>
+        <v>194</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>134</v>
+        <v>241</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>21</v>
@@ -4100,25 +4134,25 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>207</v>
+        <v>240</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>21</v>
+        <v>175</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>204</v>
+        <v>243</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>21</v>
@@ -4129,46 +4163,42 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>209</v>
+        <v>21</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>133</v>
+        <v>200</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>21</v>
       </c>
@@ -4216,25 +4246,25 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>130</v>
+        <v>204</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>21</v>
@@ -4245,21 +4275,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>21</v>
@@ -4271,15 +4301,17 @@
         <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>200</v>
+        <v>133</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>239</v>
+        <v>134</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -4328,71 +4360,75 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>238</v>
+        <v>207</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>149</v>
+        <v>204</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>241</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>21</v>
+        <v>209</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>243</v>
+        <v>133</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>244</v>
+        <v>210</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>21</v>
       </c>
@@ -4440,35 +4476,259 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>242</v>
+        <v>212</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN29" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G30" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="AI29" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
+      <c r="H30" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AK29" t="s" s="2">
+      <c r="AK30" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="AL29" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>247</v>
+      <c r="AL30" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>256</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN29">
+  <autoFilter ref="A1:AN31">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -4478,7 +4738,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI28">
+  <conditionalFormatting sqref="A2:AI30">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$48</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="349">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-10T17:53:58+00:00</t>
+    <t>2026-02-12T16:23:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,8 +87,15 @@
     <t>Description</t>
   </si>
   <si>
-    <t>**Beschreibung:** Bildet ein Arzneimittel ab, das nicht über eine PZN verfügt, z.B. magistrale Zubereitungen ("Medication"-Ressource).
-Wird die Ressource nur für magistrale Zubreitungen verwendet? Wirkstoffverschreibung? manufacturer immer ATAPSOrganization?</t>
+    <t xml:space="preserve">**Beschreibung:** Bildet ein Arzneimittel in der "Medication"-Ressource ab. Wird grundsätzlich verwendet in Planeintrag, geplante Abgabe und durchgeführte Abgabe. Aktuell nur geprüft im Kontext Planeintrag.
+Unterschieden werden folgende Fälle:
+1. Arzneimittel besitzt eine PZN und wird über diese identifiziert, die weiteren Informationen werden durch die Fachanwendung angereichert.
+    a. Identifikation nur über PZN: eine Befüllung jener Felder, die über die ASP-Liste angereichert werden können, durch den GDA wird technisch verhindert (Invariante oder eigene Medication Ressource).
+    b. Identifikation über PZN und Handelsname: damit eine Prüfung auf Übereinstimmung durchgeführt werden kann. TODO: Juristisch zu prüfen. 
+3. Arzneimittel besitzt keine PZN, alle benötigten Informationen sind verpflichtend vom GDA zu befüllen:
+    a. Bei Verschreibung von Wirkstoffen
+    b. Bei magistraler Anwendung, Infusionen 
+</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -479,7 +486,7 @@
 </t>
   </si>
   <si>
-    <t>Eindeutiger Identifikator für das Arzneimittel. Verwendung für magistrale Zubereitungen prüfen.</t>
+    <t>Eindeutiger Identifikator für das Arzneimittel. Wird nicht benötigt, da PZN, sofern vorhanden, im Code angegeben wird.</t>
   </si>
   <si>
     <t>Business identifier for this medication.</t>
@@ -501,7 +508,12 @@
 </t>
   </si>
   <si>
-    <t>Code des Arzneimittels. Verwendung für magistrale Zubereitungen prüfen.</t>
+    <t>Code des Arzneimittels. Hier muss die Pharmazentralnummer (PZN) aus der ASP-Liste angegeben werden, sofern vorhanden.
+TODO: Slicing für meherere Codings
+Gem. CDA V3: 
+Das Codesystem Pharmazentralnummer {1.2.40.0.34.4.16} wird am Terminologieserver in der ASP-Liste (Liste der humanen Arzneispezialitäten gelistet nach PZN) publiziert, 
+die ASP-Liste enthält neben der Pharmazentralnummer {1.2.40.0.34.4.17} auch die korrespondierende Zulassungsnummer und Package Reference Number der AGES {1.2.40.0.34.4.26}. 
+Für die Kompatibilität zum EU Kontext wird zukünftig auch die PCID der EMA {1.2.40.0.34.4.27} ermöglicht.</t>
   </si>
   <si>
     <t>A code (or set of codes) that specify this medication, or a textual description if no code is available. Usage note: This could be a standard medication code such as a code from RxNorm, SNOMED CT, IDMP etc. It could also be a national or local formulary code, optionally with translations to other code systems.</t>
@@ -510,13 +522,10 @@
     <t>Depending on the context of use, the code that was actually selected by the user (prescriber, dispenser, etc.) will have the coding.userSelected set to true.  As described in the coding datatype: "A coding may be marked as a "userSelected" if a user selected the particular coded value in a user interface (e.g. the user selects an item in a pick-list). If a user selected coding exists, it is the preferred choice for performing translations etc. Other codes can only be literal translations to alternative code systems, or codes at a lower level of granularity (e.g. a generic code for a vendor-specific primary one).</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>A coded concept that defines the type of a medication.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
+    <t>required</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/CodeSystem/asp-liste</t>
   </si>
   <si>
     <t>coding.code = //element(*,MedicationType)/DrugCoded/ProductCode@@ -535,10 +544,223 @@
     <t>RXO-1.1-Requested Give Code.code / RXE-2.1-Give Code.code / RXD-2.1-Dispense/Give Code.code / RXG-4.1-Give Code.code /RXA-5.1-Administered Code.code / RXC-2.1 Component Code</t>
   </si>
   <si>
+    <t>Medication.code.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Medication.code.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Medication.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>Medication.code.coding.id</t>
+  </si>
+  <si>
+    <t>Medication.code.coding.extension</t>
+  </si>
+  <si>
+    <t>Medication.code.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>Medication.code.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>Medication.code.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>Medication.code.coding.display</t>
+  </si>
+  <si>
+    <t>Juristisch zu prüfen, ob mindestens ein Displayname (Handelsname) zur PZN angegeben werden muss (Zwecks Prüfung auf Übereinstimmung und 
+historischer Verfügbarkeit, im Falle von sich ändernden PZNs; evtl. könnte die Fachanwendung.</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>Medication.code.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>Medication.code.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
     <t>Medication.status</t>
   </si>
   <si>
-    <t>Verfügbarkeitsstatus des Arzneimittels:(req) active | inactive | entered-in-error. Verwendung für magistrale Zubereitungen prüfen</t>
+    <t>Verfügbarkeitsstatus des Arzneimittels:(req) active | inactive | entered-in-error. https://hl7.org/fhir/R4/valueset-medication-status.html.
+ Keine Verwendung im Kontext Planeintrag.</t>
   </si>
   <si>
     <t>A code to indicate if the medication is in active use.</t>
@@ -547,9 +769,6 @@
     <t>This status is intended to identify if the medication in a local system is in active use within a drug database or inventory.  For example, a pharmacy system may create a new drug file record for a compounded product "ABC Hospital Special Cream" with an active status.  At some point in the future, it may be determined that the drug record was created with an error and the status is changed to "entered in error".   This status is not intended to specify if a medication is part of a particular formulary.  It is possible that the drug record may be referenced by multiple formularies or catalogues and each of those entries would have a separate status.</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
     <t>A coded concept defining if the medication is in active use.</t>
   </si>
   <si>
@@ -562,11 +781,11 @@
     <t>Medication.manufacturer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
-    <t>Der Hersteller des Arzneimittels. Für magistrale Zubereitungen die Apotheke (1..1?)</t>
+    <t>Der Hersteller des Arzneimittels. Keine Verwendung im Kontext Planeintrag. TODO: Prüfen, ob im Kontext durchgeführte Abgabe und magistraler Zubereitung erforderlich; prüfen ob Einschränkung auf österr. Organisation</t>
   </si>
   <si>
     <t>Describes the details of the manufacturer of the medication product.  This is not intended to represent the distributor of a medication product.</t>
@@ -587,7 +806,10 @@
     <t>Medication.form</t>
   </si>
   <si>
-    <t>Die Darreichungsform des Arzneimittels: (ex) powder | tablets | capsule + https://hl7.org/fhir/R4/valueset-medication-form-codes.html</t>
+    <t>Die Darreichungsform des Arzneimittels. Wenn PZN vorhanden 0..0, da Anreicherung aus ASP-Liste durch Fachanwendung.
+Gem. CDA V3: 
+Für die e-Medikation ist das CodeSystem ​Medikation_Darreichungsform 1.2.40.0.10.1.4.3.4.3.5 zu verwenden.
+Für den eHDSI Kontext ist das CodeSystem 0.4.0.127.0.16.1.1.2.1 zu verwenden.</t>
   </si>
   <si>
     <t>Describes the form of the item.  Powder; tablets; capsule.</t>
@@ -596,10 +818,7 @@
     <t>When Medication is referenced from MedicationRequest, this is the ordered form.  When Medication is referenced within MedicationDispense, this is the dispensed form.  When Medication is referenced within MedicationAdministration, this is administered form.</t>
   </si>
   <si>
-    <t>A coded concept defining the form of a medication.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-form-codes|4.0.1</t>
+    <t>https://termgit.elga.gv.at/ValueSet-elga-medikationmengenart.html</t>
   </si>
   <si>
     <t>coding.code =  //element(*,DrugCodedType)/FormCode@@ -620,7 +839,8 @@
 </t>
   </si>
   <si>
-    <t>Die Gesamtmenge des Arzneimittels in der Verpackung.</t>
+    <t>Die Gesamtmenge des Arzneimittels in der Verpackung. 
+Wenn PZN vorhanden 0..0, da Anreicherung aus ASP-Liste durch Fachanwendung.</t>
   </si>
   <si>
     <t>Specific amount of the drug in the packaged product.  For example, when specifying a product that has the same strength (For example, Insulin glargine 100 unit per mL solution for injection), this attribute provides additional clarification of the package amount (For example, 3 mL, 10mL, etc.).</t>
@@ -636,7 +856,9 @@
 </t>
   </si>
   <si>
-    <t>Active or inactive ingredient</t>
+    <t>Wirkstoffe. Wenn PZN vorhanden 0..0, da Anreicherung aus ASP-Liste durch Fachanwendung.
+Gemäß AG: Einschränkung auf CodeableConcept, TODO: prüfen, wie Freitext bei magistraler Zubereitung abgebildet wird:
+In diesem Fall müsste in einer Substance-Ressource die description (string) befüllt werden.</t>
   </si>
   <si>
     <t>Identifies a particular constituent of interest in the product.</t>
@@ -651,29 +873,7 @@
     <t>Medication.ingredient.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Medication.ingredient.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Medication.ingredient.modifierExtension</t>
@@ -697,7 +897,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Substance|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-medication)</t>
+Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-substance)</t>
   </si>
   <si>
     <t>The actual ingredient or content</t>
@@ -728,7 +928,11 @@
     <t>itemCodeableConcept</t>
   </si>
   <si>
-    <t>Inhaltsstoff codiert</t>
+    <t>Inhaltsstoff codiert. TODO: prüfen, Einschränkung auf SPOR (EMA). Gemüß CDA v3:
+Wirkstoff-Codes stammen aus der ATC-Klassifikation (Anatomical Therapeutic Chemical Classification), die von der WHO herausgegeben wird. 
+Weitere Codes, wie auch die deutsche Bezeichnung der Codes, entsprechen dem GKV-Arzneimittelindex im Wissenschaftlichen Institut der AOK (WidO), 
+AOK Bundesverband GbR, Deutschland, welcher auf den WHO ATC basiert.
+Zusätzlich kommen ergänzende Codes aus dem Arzneimittelverzeichnis der AGES zum Einsatz.</t>
   </si>
   <si>
     <t>Medication.ingredient.item[x]:itemReference</t>
@@ -737,18 +941,122 @@
     <t>itemReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Substance|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-medication)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-substance)
 </t>
   </si>
   <si>
-    <t>Referenz auf Ressourcen Substance oder Medication</t>
+    <t>Referenz auf Ressourcen Substance im Fall von magistraler Anwendung</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemReference.id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemReference.extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemReference.reference</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].reference</t>
+  </si>
+  <si>
+    <t>Literal reference, Relative, internal or absolute URL</t>
+  </si>
+  <si>
+    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
+  </si>
+  <si>
+    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
+  </si>
+  <si>
+    <t>Reference.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ref-1
+</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+contained-sub:Substance must be contained {reference.startsWith('#')}</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemReference.type</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].type</t>
+  </si>
+  <si>
+    <t>Type the reference refers to (e.g. "Patient")</t>
+  </si>
+  <si>
+    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
+The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
+  </si>
+  <si>
+    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
+  </si>
+  <si>
+    <t>Reference.type</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemReference.identifier</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].identifier</t>
+  </si>
+  <si>
+    <t>Logical reference, when literal reference is not known</t>
+  </si>
+  <si>
+    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
+  </si>
+  <si>
+    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
+When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
+Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
+Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
+  </si>
+  <si>
+    <t>Reference.identifier</t>
+  </si>
+  <si>
+    <t>.identifier</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemReference.display</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].display</t>
+  </si>
+  <si>
+    <t>Text alternative for the resource</t>
+  </si>
+  <si>
+    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
+  </si>
+  <si>
+    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
+  </si>
+  <si>
+    <t>Reference.display</t>
   </si>
   <si>
     <t>Medication.ingredient.isActive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
   </si>
   <si>
     <t>Aktive Wirkstoff TRUE/FALSE</t>
@@ -782,7 +1090,7 @@
     <t>Medication.batch</t>
   </si>
   <si>
-    <t>Informationen zur Charge des Arzneimittels. Verwendung für magistrale Zubereitungen prüfen.</t>
+    <t>Informationen zur Charge des Arzneimittels. Keine Verwenund im Kontext Planeintrag.</t>
   </si>
   <si>
     <t>Information that only applies to packages (not products).</t>
@@ -803,7 +1111,7 @@
     <t>Medication.batch.lotNumber</t>
   </si>
   <si>
-    <t>Identifkation der Charge</t>
+    <t>Identifier assigned to batch</t>
   </si>
   <si>
     <t>The assigned lot number of a batch of the specified product.</t>
@@ -819,7 +1127,7 @@
 </t>
   </si>
   <si>
-    <t>Ablaufdatum</t>
+    <t>When batch will expire</t>
   </si>
   <si>
     <t>When this specific batch of product will expire.</t>
@@ -1153,10 +1461,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN31"/>
+  <dimension ref="A1:AN48"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="42.22265625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="44.546875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="32.79296875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="18.3359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1166,7 +1474,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="75.19140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="65.7109375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1180,11 +1488,11 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="47.4921875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="45.22265625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="51.97265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="54.3359375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -2359,7 +2667,7 @@
         <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>21</v>
@@ -2457,7 +2765,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>151</v>
       </c>
@@ -2476,7 +2784,7 @@
         <v>87</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>21</v>
@@ -2522,11 +2830,9 @@
       <c r="X12" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="Y12" t="s" s="2">
+      <c r="Y12" s="2"/>
+      <c r="Z12" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>21</v>
@@ -2559,24 +2865,24 @@
         <v>99</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AL12" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="AL12" t="s" s="2">
+      <c r="AM12" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="AM12" t="s" s="2">
+      <c r="AN12" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>162</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2593,13 +2899,13 @@
         <v>21</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>107</v>
+        <v>163</v>
       </c>
       <c r="L13" t="s" s="2">
         <v>164</v>
@@ -2607,9 +2913,7 @@
       <c r="M13" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="N13" t="s" s="2">
-        <v>166</v>
-      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>21</v>
@@ -2634,13 +2938,13 @@
         <v>21</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>167</v>
+        <v>21</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>168</v>
+        <v>21</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>169</v>
+        <v>21</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>21</v>
@@ -2658,7 +2962,7 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2670,13 +2974,13 @@
         <v>21</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>21</v>
@@ -2685,43 +2989,45 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>172</v>
+        <v>133</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>173</v>
+        <v>134</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N14" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>21</v>
@@ -2758,51 +3064,51 @@
         <v>21</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>21</v>
+        <v>170</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>21</v>
+        <v>171</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>21</v>
+        <v>172</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>177</v>
+        <v>21</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>178</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2810,33 +3116,35 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J15" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J15" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K15" t="s" s="2">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="O15" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="O15" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="P15" t="s" s="2">
         <v>21</v>
       </c>
@@ -2860,13 +3168,13 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>183</v>
+        <v>21</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>184</v>
+        <v>21</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -2884,13 +3192,13 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>21</v>
@@ -2899,24 +3207,24 @@
         <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>185</v>
+        <v>21</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>187</v>
+        <v>182</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2930,22 +3238,22 @@
         <v>87</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2996,7 +3304,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3008,13 +3316,13 @@
         <v>21</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>21</v>
@@ -3023,26 +3331,26 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>21</v>
@@ -3051,16 +3359,16 @@
         <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>194</v>
+        <v>133</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>195</v>
+        <v>134</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>196</v>
+        <v>169</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>197</v>
+        <v>136</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3098,19 +3406,19 @@
         <v>21</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>21</v>
+        <v>170</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>21</v>
+        <v>171</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>21</v>
+        <v>172</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3122,13 +3430,13 @@
         <v>21</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>198</v>
+        <v>167</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>21</v>
@@ -3139,10 +3447,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3162,19 +3470,23 @@
         <v>21</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>200</v>
+        <v>101</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
+        <v>187</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>21</v>
       </c>
@@ -3222,7 +3534,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3234,38 +3546,38 @@
         <v>21</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>21</v>
+        <v>192</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>21</v>
@@ -3274,19 +3586,19 @@
         <v>21</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>134</v>
+        <v>194</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>136</v>
+        <v>196</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3336,74 +3648,72 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>21</v>
+        <v>199</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>209</v>
+        <v>21</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>142</v>
+        <v>203</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>21</v>
@@ -3452,39 +3762,39 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>130</v>
+        <v>205</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>21</v>
+        <v>206</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3492,7 +3802,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>87</v>
@@ -3504,20 +3814,20 @@
         <v>21</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>214</v>
+        <v>163</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>21</v>
@@ -3554,20 +3864,22 @@
         <v>21</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="AC21" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>219</v>
+        <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>87</v>
@@ -3579,28 +3891,26 @@
         <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>221</v>
+        <v>213</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>223</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>21</v>
       </c>
@@ -3612,26 +3922,28 @@
         <v>87</v>
       </c>
       <c r="H22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J22" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J22" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K22" t="s" s="2">
-        <v>152</v>
+        <v>215</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="O22" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -3680,10 +3992,10 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>87</v>
@@ -3695,28 +4007,26 @@
         <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>21</v>
       </c>
@@ -3728,26 +4038,28 @@
         <v>87</v>
       </c>
       <c r="H23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J23" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J23" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K23" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="O23" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>21</v>
@@ -3796,10 +4108,10 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>87</v>
@@ -3811,24 +4123,24 @@
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>221</v>
+        <v>230</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3839,30 +4151,30 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I24" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I24" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="J24" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>230</v>
+        <v>107</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" t="s" s="2">
         <v>233</v>
       </c>
+      <c r="N24" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>21</v>
       </c>
@@ -3886,13 +4198,13 @@
         <v>21</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>21</v>
+        <v>235</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>21</v>
+        <v>236</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
@@ -3910,7 +4222,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -3928,7 +4240,7 @@
         <v>21</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>21</v>
@@ -3937,12 +4249,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3953,25 +4265,25 @@
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J25" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K25" t="s" s="2">
-        <v>189</v>
+        <v>239</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4022,7 +4334,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4037,24 +4349,24 @@
         <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>192</v>
+        <v>243</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>21</v>
+        <v>244</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>239</v>
+        <v>245</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4077,15 +4389,17 @@
         <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>194</v>
+        <v>152</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>21</v>
@@ -4110,13 +4424,11 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>21</v>
+        <v>250</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -4134,7 +4446,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4149,24 +4461,24 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>175</v>
+        <v>251</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>21</v>
+        <v>253</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4180,22 +4492,22 @@
         <v>87</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>200</v>
+        <v>255</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>201</v>
+        <v>256</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>202</v>
+        <v>257</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4246,7 +4558,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>203</v>
+        <v>254</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4258,13 +4570,13 @@
         <v>21</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>204</v>
+        <v>258</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>21</v>
@@ -4273,16 +4585,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4292,7 +4604,7 @@
         <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>21</v>
@@ -4301,16 +4613,16 @@
         <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>133</v>
+        <v>260</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>134</v>
+        <v>261</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>206</v>
+        <v>262</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>136</v>
+        <v>263</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4360,7 +4672,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>207</v>
+        <v>259</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4372,13 +4684,13 @@
         <v>21</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>204</v>
+        <v>264</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>21</v>
@@ -4389,46 +4701,42 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>209</v>
+        <v>21</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>210</v>
+        <v>164</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>21</v>
       </c>
@@ -4476,25 +4784,25 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>212</v>
+        <v>166</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>130</v>
+        <v>167</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>21</v>
@@ -4503,26 +4811,26 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>21</v>
@@ -4531,15 +4839,17 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>200</v>
+        <v>133</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>248</v>
+        <v>134</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -4588,71 +4898,75 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>247</v>
+        <v>173</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>250</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>21</v>
+        <v>268</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I31" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I31" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="J31" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>252</v>
+        <v>133</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>270</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>21</v>
       </c>
@@ -4700,35 +5014,1965 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" hidden="true">
+      <c r="A32" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="AI31" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
+      <c r="G32" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="P32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AC32" s="2"/>
+      <c r="AD32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AK31" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AL31" t="s" s="2">
+      <c r="AK32" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="D33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="P33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="D34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="P34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="35" hidden="true">
+      <c r="A35" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" hidden="true">
+      <c r="A36" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O36" s="2"/>
+      <c r="P36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" hidden="true">
+      <c r="A37" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" hidden="true">
+      <c r="A38" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="O38" s="2"/>
+      <c r="P38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" hidden="true">
+      <c r="A39" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="O39" s="2"/>
+      <c r="P39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" hidden="true">
+      <c r="A40" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="O40" s="2"/>
+      <c r="P40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="P41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K42" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="AM31" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>256</v>
+      <c r="L42" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="43" hidden="true">
+      <c r="A43" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="44" hidden="true">
+      <c r="A44" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45" hidden="true">
+      <c r="A45" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="P46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="47" hidden="true">
+      <c r="A47" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
+      <c r="P47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="48" hidden="true">
+      <c r="A48" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+      <c r="P48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>348</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN31">
+  <autoFilter ref="A1:AN48">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -4738,7 +6982,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI30">
+  <conditionalFormatting sqref="A2:AI47">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-12T16:23:56+00:00</t>
+    <t>2026-02-16T10:10:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T10:10:16+00:00</t>
+    <t>2026-02-16T15:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -395,7 +395,7 @@
 </t>
   </si>
   <si>
-    <t>Text summary of the resource, for human interpretation</t>
+    <t>TODO: Freitext für magistrale Anwendungen oder Abbildung in Substance.description?</t>
   </si>
   <si>
     <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
@@ -785,7 +785,8 @@
 </t>
   </si>
   <si>
-    <t>Der Hersteller des Arzneimittels. Keine Verwendung im Kontext Planeintrag. TODO: Prüfen, ob im Kontext durchgeführte Abgabe und magistraler Zubereitung erforderlich; prüfen ob Einschränkung auf österr. Organisation</t>
+    <t>Der Hersteller des Arzneimittels. Keine Verwendung im Kontext Planeintrag. 
+TODO: Prüfen, ob im Kontext durchgeführte Abgabe und magistraler Zubereitung erforderlich; HL7ATCoreOrganization schränkt auf Organisationen gemäß GDA-Index ein.</t>
   </si>
   <si>
     <t>Describes the details of the manufacturer of the medication product.  This is not intended to represent the distributor of a medication product.</t>
@@ -858,7 +859,7 @@
   <si>
     <t>Wirkstoffe. Wenn PZN vorhanden 0..0, da Anreicherung aus ASP-Liste durch Fachanwendung.
 Gemäß AG: Einschränkung auf CodeableConcept, TODO: prüfen, wie Freitext bei magistraler Zubereitung abgebildet wird:
-In diesem Fall müsste in einer Substance-Ressource die description (string) befüllt werden.</t>
+Evtl. in einer Substance-Ressource in der description (string).</t>
   </si>
   <si>
     <t>Identifies a particular constituent of interest in the product.</t>
@@ -2193,7 +2194,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>115</v>
       </c>
@@ -2212,7 +2213,7 @@
         <v>87</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T15:59:40+00:00</t>
+    <t>2026-02-17T17:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T17:15:57+00:00</t>
+    <t>2026-02-20T10:02:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T10:02:53+00:00</t>
+    <t>2026-02-23T08:57:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -819,7 +819,7 @@
     <t>When Medication is referenced from MedicationRequest, this is the ordered form.  When Medication is referenced within MedicationDispense, this is the dispensed form.  When Medication is referenced within MedicationAdministration, this is administered form.</t>
   </si>
   <si>
-    <t>https://termgit.elga.gv.at/ValueSet-elga-medikationmengenart.html</t>
+    <t>https://termgit.elga.gv.at/ValueSet-elga-medikationmengenart</t>
   </si>
   <si>
     <t>coding.code =  //element(*,DrugCodedType)/FormCode@@ -1490,7 +1490,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="51.97265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="54.3359375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.2578125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T08:57:08+00:00</t>
+    <t>2026-02-23T17:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T17:25:44+00:00</t>
+    <t>2026-02-26T16:36:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t xml:space="preserve">**Beschreibung:** Bildet ein Arzneimittel in der "Medication"-Ressource ab. Wird grundsätzlich verwendet in Planeintrag, geplante Abgabe und durchgeführte Abgabe. Aktuell nur geprüft im Kontext Planeintrag.
+    <t xml:space="preserve">Bildet ein Arzneimittel in der "Medication"-Ressource ab. Wird grundsätzlich verwendet in Planeintrag, geplante Abgabe und durchgeführte Abgabe. Aktuell nur geprüft im Kontext Planeintrag.
 Unterschieden werden folgende Fälle:
 1. Arzneimittel besitzt eine PZN und wird über diese identifiziert, die weiteren Informationen werden durch die Fachanwendung angereichert.
     a. Identifikation nur über PZN: eine Befüllung jener Felder, die über die ASP-Liste angereichert werden können, durch den GDA wird technisch verhindert (Invariante oder eigene Medication Ressource).

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T16:36:39+00:00</t>
+    <t>2026-03-03T08:59:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T08:59:33+00:00</t>
+    <t>2026-03-03T14:03:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T14:03:22+00:00</t>
+    <t>2026-03-05T12:55:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T12:55:37+00:00</t>
+    <t>2026-03-05T13:31:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T13:31:59+00:00</t>
+    <t>2026-03-06T12:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T12:22:28+00:00</t>
+    <t>2026-03-06T14:18:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T14:18:10+00:00</t>
+    <t>2026-03-09T08:14:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T08:14:04+00:00</t>
+    <t>2026-03-09T10:03:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T10:03:26+00:00</t>
+    <t>2026-03-09T11:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T11:27:52+00:00</t>
+    <t>2026-03-10T08:28:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T08:28:41+00:00</t>
+    <t>2026-03-10T11:00:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T11:00:19+00:00</t>
+    <t>2026-03-10T11:31:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$42</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1549" uniqueCount="315">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T11:31:06+00:00</t>
+    <t>2026-03-16T16:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -898,7 +898,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-substance)</t>
+Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-substance) &lt;&lt;contained&gt;&gt;</t>
   </si>
   <si>
     <t>The actual ingredient or content</t>
@@ -942,119 +942,11 @@
     <t>itemReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-substance)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-substance) &lt;&lt;contained&gt;&gt;
 </t>
   </si>
   <si>
     <t>Referenz auf Ressourcen Substance im Fall von magistraler Anwendung</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x]:itemReference.id</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].id</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x]:itemReference.extension</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].extension</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x]:itemReference.reference</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].reference</t>
-  </si>
-  <si>
-    <t>Literal reference, Relative, internal or absolute URL</t>
-  </si>
-  <si>
-    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
-  </si>
-  <si>
-    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
-  </si>
-  <si>
-    <t>Reference.reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ref-1
-</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-contained-sub:Substance must be contained {reference.startsWith('#')}</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x]:itemReference.type</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].type</t>
-  </si>
-  <si>
-    <t>Type the reference refers to (e.g. "Patient")</t>
-  </si>
-  <si>
-    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
-The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
-  </si>
-  <si>
-    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
-  </si>
-  <si>
-    <t>Reference.type</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x]:itemReference.identifier</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].identifier</t>
-  </si>
-  <si>
-    <t>Logical reference, when literal reference is not known</t>
-  </si>
-  <si>
-    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
-  </si>
-  <si>
-    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
-When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
-Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
-Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
-  </si>
-  <si>
-    <t>Reference.identifier</t>
-  </si>
-  <si>
-    <t>.identifier</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x]:itemReference.display</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].display</t>
-  </si>
-  <si>
-    <t>Text alternative for the resource</t>
-  </si>
-  <si>
-    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
-  </si>
-  <si>
-    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
-  </si>
-  <si>
-    <t>Reference.display</t>
   </si>
   <si>
     <t>Medication.ingredient.isActive</t>
@@ -1462,10 +1354,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN48"/>
+  <dimension ref="A1:AN42"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="44.546875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="42.22265625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="32.79296875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="18.3359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1475,7 +1367,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="65.7109375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="79.27734375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1489,7 +1381,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="51.97265625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="47.4921875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="50.2578125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -5386,12 +5278,12 @@
         <v>280</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>288</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5405,7 +5297,7 @@
         <v>87</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>21</v>
@@ -5414,16 +5306,18 @@
         <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>163</v>
+        <v>215</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>164</v>
+        <v>289</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>165</v>
+        <v>290</v>
       </c>
       <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+      <c r="O35" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>21</v>
       </c>
@@ -5471,7 +5365,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>166</v>
+        <v>288</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5483,13 +5377,13 @@
         <v>21</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>167</v>
+        <v>292</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>21</v>
@@ -5498,26 +5392,26 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>21</v>
@@ -5526,17 +5420,15 @@
         <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>133</v>
+        <v>255</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>134</v>
+        <v>294</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>21</v>
@@ -5573,51 +5465,51 @@
         <v>21</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>170</v>
+        <v>21</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>173</v>
+        <v>293</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>21</v>
+        <v>296</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>167</v>
+        <v>258</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>21</v>
+        <v>297</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5628,7 +5520,7 @@
         <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>21</v>
@@ -5637,20 +5529,18 @@
         <v>21</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>163</v>
+        <v>260</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -5699,7 +5589,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5708,16 +5598,16 @@
         <v>87</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>298</v>
+        <v>21</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>299</v>
+        <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>21</v>
+        <v>242</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>130</v>
+        <v>301</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>21</v>
@@ -5728,10 +5618,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5751,20 +5641,18 @@
         <v>21</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>101</v>
+        <v>163</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>302</v>
+        <v>164</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>21</v>
@@ -5789,13 +5677,13 @@
         <v>21</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>305</v>
+        <v>21</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>306</v>
+        <v>21</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>307</v>
+        <v>21</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>21</v>
@@ -5813,7 +5701,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>308</v>
+        <v>166</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5825,13 +5713,13 @@
         <v>21</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>130</v>
+        <v>167</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>21</v>
@@ -5842,21 +5730,21 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>21</v>
@@ -5865,19 +5753,19 @@
         <v>21</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>311</v>
+        <v>134</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>312</v>
+        <v>169</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>313</v>
+        <v>136</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5927,25 +5815,25 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>314</v>
+        <v>173</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>315</v>
+        <v>167</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>21</v>
@@ -5956,44 +5844,46 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>21</v>
+        <v>268</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J40" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>318</v>
+        <v>269</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>319</v>
+        <v>270</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>136</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>21</v>
       </c>
@@ -6041,19 +5931,19 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>321</v>
+        <v>271</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>21</v>
@@ -6068,12 +5958,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6087,7 +5977,7 @@
         <v>87</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>21</v>
@@ -6096,18 +5986,16 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>215</v>
+        <v>163</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>323</v>
+        <v>306</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="N41" s="2"/>
-      <c r="O41" t="s" s="2">
-        <v>325</v>
-      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>21</v>
       </c>
@@ -6155,7 +6043,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6170,24 +6058,24 @@
         <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>21</v>
+        <v>242</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>326</v>
+        <v>149</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>21</v>
+        <v>308</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>327</v>
+        <v>309</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>327</v>
+        <v>309</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6201,7 +6089,7 @@
         <v>87</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>21</v>
@@ -6210,13 +6098,13 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>255</v>
+        <v>310</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6267,7 +6155,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>327</v>
+        <v>309</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6282,698 +6170,20 @@
         <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>330</v>
+        <v>242</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>258</v>
+        <v>313</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="43" hidden="true">
-      <c r="A43" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="C43" s="2"/>
-      <c r="D43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E43" s="2"/>
-      <c r="F43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K43" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
-      <c r="P43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q43" s="2"/>
-      <c r="R43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="44" hidden="true">
-      <c r="A44" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="C44" s="2"/>
-      <c r="D44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E44" s="2"/>
-      <c r="F44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G44" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K44" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
-      <c r="P44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q44" s="2"/>
-      <c r="R44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="45" hidden="true">
-      <c r="A45" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="C45" s="2"/>
-      <c r="D45" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="E45" s="2"/>
-      <c r="F45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K45" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O45" s="2"/>
-      <c r="P45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q45" s="2"/>
-      <c r="R45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="46" hidden="true">
-      <c r="A46" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="C46" s="2"/>
-      <c r="D46" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="E46" s="2"/>
-      <c r="F46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K46" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="P46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q46" s="2"/>
-      <c r="R46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="47" hidden="true">
-      <c r="A47" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="C47" s="2"/>
-      <c r="D47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E47" s="2"/>
-      <c r="F47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G47" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K47" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
-      <c r="P47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q47" s="2"/>
-      <c r="R47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="48" hidden="true">
-      <c r="A48" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="C48" s="2"/>
-      <c r="D48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E48" s="2"/>
-      <c r="F48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G48" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K48" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
-      <c r="P48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q48" s="2"/>
-      <c r="R48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="AG48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>348</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN48">
+  <autoFilter ref="A1:AN42">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -6983,7 +6193,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI47">
+  <conditionalFormatting sqref="A2:AI41">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T16:50:24+00:00</t>
+    <t>2026-03-19T16:44:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T16:44:44+00:00</t>
+    <t>2026-03-20T13:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T13:50:58+00:00</t>
+    <t>2026-03-20T15:30:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T15:30:14+00:00</t>
+    <t>2026-03-24T10:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T10:00:40+00:00</t>
+    <t>2026-03-24T15:12:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T15:12:36+00:00</t>
+    <t>2026-03-27T10:18:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T10:18:57+00:00</t>
+    <t>2026-03-30T07:39:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T07:39:16+00:00</t>
+    <t>2026-03-30T10:13:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T10:13:35+00:00</t>
+    <t>2026-04-01T13:59:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T13:59:59+00:00</t>
+    <t>2026-04-02T15:01:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T15:01:02+00:00</t>
+    <t>2026-04-07T09:06:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T09:06:22+00:00</t>
+    <t>2026-04-07T15:41:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T15:41:53+00:00</t>
+    <t>2026-04-07T16:09:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T16:09:01+00:00</t>
+    <t>2026-04-08T18:33:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T18:33:44+00:00</t>
+    <t>2026-04-09T06:40:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T06:40:16+00:00</t>
+    <t>2026-04-09T18:30:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T18:30:31+00:00</t>
+    <t>2026-04-10T11:48:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T11:48:51+00:00</t>
+    <t>2026-04-13T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T14:44:53+00:00</t>
+    <t>2026-04-13T15:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T15:27:52+00:00</t>
+    <t>2026-04-13T20:12:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T20:12:42+00:00</t>
+    <t>2026-04-14T10:13:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T10:13:14+00:00</t>
+    <t>2026-04-17T19:15:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T19:15:07+00:00</t>
+    <t>2026-04-20T08:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1549" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1549" uniqueCount="314">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T08:20:06+00:00</t>
+    <t>2026-04-20T16:24:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,15 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t xml:space="preserve">Bildet ein Arzneimittel in der "Medication"-Ressource ab. Wird grundsätzlich verwendet in Planeintrag, geplante Abgabe und durchgeführte Abgabe. Aktuell nur geprüft im Kontext Planeintrag.
-Unterschieden werden folgende Fälle:
-1. Arzneimittel besitzt eine PZN und wird über diese identifiziert, die weiteren Informationen werden durch die Fachanwendung angereichert.
-    a. Identifikation nur über PZN: eine Befüllung jener Felder, die über die ASP-Liste angereichert werden können, durch den GDA wird technisch verhindert (Invariante oder eigene Medication Ressource).
-    b. Identifikation über PZN und Handelsname: damit eine Prüfung auf Übereinstimmung durchgeführt werden kann. TODO: Juristisch zu prüfen. 
-3. Arzneimittel besitzt keine PZN, alle benötigten Informationen sind verpflichtend vom GDA zu befüllen:
-    a. Bei Verschreibung von Wirkstoffen
-    b. Bei magistraler Anwendung, Infusionen 
-</t>
+    <t>Bildet ein Arzneimittel in der "Medication"-Ressource ab. Wird grundsätzlich verwendet in Planeintrag, geplante Abgabe und durchgeführte Abgabe.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -857,9 +849,7 @@
 </t>
   </si>
   <si>
-    <t>Wirkstoffe. Wenn PZN vorhanden 0..0, da Anreicherung aus ASP-Liste durch Fachanwendung.
-Gemäß AG: Einschränkung auf CodeableConcept, TODO: prüfen, wie Freitext bei magistraler Zubereitung abgebildet wird:
-Evtl. in einer Substance-Ressource in der description (string).</t>
+    <t>Wirkstoffe. Keine Angabe, wenn PZN vorhanden (Anreicherung aus ASP-Liste durch Fachanwendung).</t>
   </si>
   <si>
     <t>Identifies a particular constituent of interest in the product.</t>
@@ -929,13 +919,6 @@
     <t>itemCodeableConcept</t>
   </si>
   <si>
-    <t>Inhaltsstoff codiert. TODO: prüfen, Einschränkung auf SPOR (EMA). Gemüß CDA v3:
-Wirkstoff-Codes stammen aus der ATC-Klassifikation (Anatomical Therapeutic Chemical Classification), die von der WHO herausgegeben wird. 
-Weitere Codes, wie auch die deutsche Bezeichnung der Codes, entsprechen dem GKV-Arzneimittelindex im Wissenschaftlichen Institut der AOK (WidO), 
-AOK Bundesverband GbR, Deutschland, welcher auf den WHO ATC basiert.
-Zusätzlich kommen ergänzende Codes aus dem Arzneimittelverzeichnis der AGES zum Einsatz.</t>
-  </si>
-  <si>
     <t>Medication.ingredient.item[x]:itemReference</t>
   </si>
   <si>
@@ -968,7 +951,7 @@
     <t>Medication.ingredient.strength</t>
   </si>
   <si>
-    <t>Menge der vorhandenen Zutat</t>
+    <t>Menge der vorhandenen Zutaten.</t>
   </si>
   <si>
     <t>Specifies how many (or how much) of the items there are in this Medication.  For example, 250 mg per tablet.  This is expressed as a ratio where the numerator is 250mg and the denominator is 1 tablet.</t>
@@ -983,7 +966,7 @@
     <t>Medication.batch</t>
   </si>
   <si>
-    <t>Informationen zur Charge des Arzneimittels. Keine Verwenund im Kontext Planeintrag.</t>
+    <t>Informationen zur Charge des Arzneimittels.</t>
   </si>
   <si>
     <t>Information that only applies to packages (not products).</t>
@@ -5079,7 +5062,7 @@
         <v>152</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="M33" t="s" s="2">
         <v>275</v>
@@ -5164,13 +5147,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>272</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>21</v>
@@ -5192,10 +5175,10 @@
         <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="L34" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="M34" t="s" s="2">
         <v>275</v>
@@ -5280,10 +5263,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5309,14 +5292,14 @@
         <v>215</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>21</v>
@@ -5365,7 +5348,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5383,7 +5366,7 @@
         <v>21</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>21</v>
@@ -5394,10 +5377,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5423,10 +5406,10 @@
         <v>255</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5477,7 +5460,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5492,7 +5475,7 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>258</v>
@@ -5501,15 +5484,15 @@
         <v>21</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5535,10 +5518,10 @@
         <v>260</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5589,7 +5572,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5607,7 +5590,7 @@
         <v>242</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>21</v>
@@ -5618,10 +5601,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5730,10 +5713,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5844,10 +5827,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5960,10 +5943,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5989,10 +5972,10 @@
         <v>163</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6043,7 +6026,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6067,15 +6050,15 @@
         <v>21</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6098,13 +6081,13 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6155,7 +6138,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6173,13 +6156,13 @@
         <v>242</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>314</v>
       </c>
     </row>
   </sheetData>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T16:24:35+00:00</t>
+    <t>2026-04-20T19:04:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T19:04:12+00:00</t>
+    <t>2026-04-21T08:44:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T08:44:51+00:00</t>
+    <t>2026-04-21T11:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T11:54:48+00:00</t>
+    <t>2026-04-21T14:09:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T14:09:10+00:00</t>
+    <t>2026-04-21T17:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T17:01:26+00:00</t>
+    <t>2026-04-22T08:49:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T08:49:17+00:00</t>
+    <t>2026-04-22T10:01:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$31</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1549" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="253">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T10:01:54+00:00</t>
+    <t>2026-04-22T10:11:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -387,7 +387,7 @@
 </t>
   </si>
   <si>
-    <t>TODO: Freitext für magistrale Anwendungen oder Abbildung in Substance.description?</t>
+    <t>Text summary of the resource, for human interpretation</t>
   </si>
   <si>
     <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
@@ -500,12 +500,7 @@
 </t>
   </si>
   <si>
-    <t>Code des Arzneimittels. Hier muss die Pharmazentralnummer (PZN) aus der ASP-Liste angegeben werden, sofern vorhanden.
-TODO: Slicing für meherere Codings
-Gem. CDA V3: 
-Das Codesystem Pharmazentralnummer {1.2.40.0.34.4.16} wird am Terminologieserver in der ASP-Liste (Liste der humanen Arzneispezialitäten gelistet nach PZN) publiziert, 
-die ASP-Liste enthält neben der Pharmazentralnummer {1.2.40.0.34.4.17} auch die korrespondierende Zulassungsnummer und Package Reference Number der AGES {1.2.40.0.34.4.26}. 
-Für die Kompatibilität zum EU Kontext wird zukünftig auch die PCID der EMA {1.2.40.0.34.4.27} ermöglicht.</t>
+    <t>Code des Arzneimittels. Hier muss die Pharmazentralnummer (PZN) aus der ASP-Liste angegeben werden, sofern vorhanden.</t>
   </si>
   <si>
     <t>A code (or set of codes) that specify this medication, or a textual description if no code is available. Usage note: This could be a standard medication code such as a code from RxNorm, SNOMED CT, IDMP etc. It could also be a national or local formulary code, optionally with translations to other code systems.</t>
@@ -536,218 +531,6 @@
     <t>RXO-1.1-Requested Give Code.code / RXE-2.1-Give Code.code / RXD-2.1-Dispense/Give Code.code / RXG-4.1-Give Code.code /RXA-5.1-Administered Code.code / RXC-2.1 Component Code</t>
   </si>
   <si>
-    <t>Medication.code.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Medication.code.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Medication.code.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>Medication.code.coding.id</t>
-  </si>
-  <si>
-    <t>Medication.code.coding.extension</t>
-  </si>
-  <si>
-    <t>Medication.code.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>Medication.code.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>Medication.code.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>Medication.code.coding.display</t>
-  </si>
-  <si>
-    <t>Juristisch zu prüfen, ob mindestens ein Displayname (Handelsname) zur PZN angegeben werden muss (Zwecks Prüfung auf Übereinstimmung und 
-historischer Verfügbarkeit, im Falle von sich ändernden PZNs; evtl. könnte die Fachanwendung.</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>Medication.code.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>Medication.code.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
     <t>Medication.status</t>
   </si>
   <si>
@@ -777,8 +560,7 @@
 </t>
   </si>
   <si>
-    <t>Der Hersteller des Arzneimittels. Keine Verwendung im Kontext Planeintrag. 
-TODO: Prüfen, ob im Kontext durchgeführte Abgabe und magistraler Zubereitung erforderlich; HL7ATCoreOrganization schränkt auf Organisationen gemäß GDA-Index ein.</t>
+    <t>Der Hersteller des Arzneimittels. Keine Verwendung im Kontext Planeintrag.</t>
   </si>
   <si>
     <t>Describes the details of the manufacturer of the medication product.  This is not intended to represent the distributor of a medication product.</t>
@@ -799,10 +581,7 @@
     <t>Medication.form</t>
   </si>
   <si>
-    <t>Die Darreichungsform des Arzneimittels. Wenn PZN vorhanden 0..0, da Anreicherung aus ASP-Liste durch Fachanwendung.
-Gem. CDA V3: 
-Für die e-Medikation ist das CodeSystem ​Medikation_Darreichungsform 1.2.40.0.10.1.4.3.4.3.5 zu verwenden.
-Für den eHDSI Kontext ist das CodeSystem 0.4.0.127.0.16.1.1.2.1 zu verwenden.</t>
+    <t>Die Darreichungsform des Arzneimittels. Wenn PZN vorhanden 0..0, da Anreicherung aus ASP-Liste durch Fachanwendung.</t>
   </si>
   <si>
     <t>Describes the form of the item.  Powder; tablets; capsule.</t>
@@ -864,7 +643,29 @@
     <t>Medication.ingredient.id</t>
   </si>
   <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>Medication.ingredient.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
   </si>
   <si>
     <t>Medication.ingredient.modifierExtension</t>
@@ -929,10 +730,14 @@
 </t>
   </si>
   <si>
-    <t>Referenz auf Ressourcen Substance im Fall von magistraler Anwendung</t>
+    <t>Referenz auf Ressourcen Substance im Fall von magistraler Anwendung.</t>
   </si>
   <si>
     <t>Medication.ingredient.isActive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
   </si>
   <si>
     <t>Aktive Wirkstoff TRUE/FALSE</t>
@@ -1337,7 +1142,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN42"/>
+  <dimension ref="A1:AN31"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="42.22265625" customWidth="true" bestFit="true"/>
@@ -1368,7 +1173,7 @@
     <col min="26" max="26" width="50.2578125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -2069,7 +1874,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>115</v>
       </c>
@@ -2088,7 +1893,7 @@
         <v>87</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>21</v>
@@ -2769,27 +2574,29 @@
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>21</v>
@@ -2814,13 +2621,13 @@
         <v>21</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>21</v>
+        <v>166</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>21</v>
+        <v>167</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>21</v>
@@ -2838,7 +2645,7 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2850,13 +2657,13 @@
         <v>21</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>21</v>
@@ -2867,21 +2674,21 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>21</v>
@@ -2890,20 +2697,18 @@
         <v>21</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>21</v>
@@ -2940,51 +2745,51 @@
         <v>21</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>170</v>
+        <v>21</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK14" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="AG14" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK14" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AL14" t="s" s="2">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>21</v>
+        <v>175</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" hidden="true">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2995,32 +2800,30 @@
         <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>175</v>
+        <v>152</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>21</v>
       </c>
@@ -3044,13 +2847,11 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>21</v>
+        <v>181</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -3068,13 +2869,13 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>21</v>
@@ -3083,24 +2884,24 @@
         <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>21</v>
+        <v>182</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="16" hidden="true">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3114,22 +2915,22 @@
         <v>87</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>164</v>
+        <v>187</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3180,7 +2981,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3192,13 +2993,13 @@
         <v>21</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>21</v>
@@ -3207,16 +3008,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3226,7 +3027,7 @@
         <v>79</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>21</v>
@@ -3235,16 +3036,16 @@
         <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>133</v>
+        <v>191</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>134</v>
+        <v>192</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>136</v>
+        <v>194</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3282,19 +3083,19 @@
         <v>21</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>170</v>
+        <v>21</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3306,13 +3107,13 @@
         <v>21</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>167</v>
+        <v>195</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>21</v>
@@ -3323,10 +3124,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3346,23 +3147,19 @@
         <v>21</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>101</v>
+        <v>197</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>21</v>
       </c>
@@ -3410,7 +3207,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3422,38 +3219,38 @@
         <v>21</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>192</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>21</v>
@@ -3462,19 +3259,19 @@
         <v>21</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>194</v>
+        <v>134</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>196</v>
+        <v>136</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3524,72 +3321,74 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>199</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>21</v>
+        <v>206</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O20" t="s" s="2">
-        <v>203</v>
+        <v>142</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>21</v>
@@ -3638,39 +3437,39 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>205</v>
+        <v>130</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>206</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3678,7 +3477,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>87</v>
@@ -3690,20 +3489,20 @@
         <v>21</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>163</v>
+        <v>211</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>21</v>
@@ -3740,22 +3539,20 @@
         <v>21</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="AC21" s="2"/>
       <c r="AD21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>21</v>
+        <v>216</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>87</v>
@@ -3767,26 +3564,28 @@
         <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>21</v>
+        <v>158</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="22" hidden="true">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>210</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="D22" t="s" s="2">
         <v>21</v>
       </c>
@@ -3798,28 +3597,26 @@
         <v>87</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>215</v>
+        <v>152</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>218</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -3868,10 +3665,10 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>87</v>
@@ -3883,26 +3680,28 @@
         <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>21</v>
+        <v>158</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AM22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN22" t="s" s="2">
+      <c r="B23" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="C23" t="s" s="2">
         <v>222</v>
       </c>
-    </row>
-    <row r="23" hidden="true">
-      <c r="A23" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>21</v>
       </c>
@@ -3914,28 +3713,26 @@
         <v>87</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>163</v>
+        <v>223</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>224</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>21</v>
@@ -3984,10 +3781,10 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>87</v>
@@ -3999,24 +3796,24 @@
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>21</v>
+        <v>158</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="24" hidden="true">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4027,30 +3824,30 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>107</v>
+        <v>226</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>21</v>
       </c>
@@ -4074,13 +3871,13 @@
         <v>21</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>235</v>
+        <v>21</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>236</v>
+        <v>21</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
@@ -4098,7 +3895,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4116,7 +3913,7 @@
         <v>21</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>21</v>
@@ -4125,12 +3922,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4141,25 +3938,25 @@
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>239</v>
+        <v>186</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4210,7 +4007,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4225,24 +4022,24 @@
         <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>243</v>
+        <v>189</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>244</v>
+        <v>21</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4253,10 +4050,10 @@
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>21</v>
@@ -4265,17 +4062,15 @@
         <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>152</v>
+        <v>191</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>21</v>
@@ -4300,11 +4095,13 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="Y26" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z26" t="s" s="2">
-        <v>250</v>
+        <v>21</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -4322,7 +4119,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4337,24 +4134,24 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>251</v>
+        <v>173</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4368,22 +4165,22 @@
         <v>87</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>255</v>
+        <v>197</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>256</v>
+        <v>198</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>257</v>
+        <v>199</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4434,7 +4231,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4446,13 +4243,13 @@
         <v>21</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>258</v>
+        <v>201</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>21</v>
@@ -4461,16 +4258,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4480,7 +4277,7 @@
         <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>21</v>
@@ -4489,16 +4286,16 @@
         <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>260</v>
+        <v>133</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>261</v>
+        <v>134</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>262</v>
+        <v>203</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>263</v>
+        <v>136</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4548,7 +4345,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>259</v>
+        <v>204</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4560,13 +4357,13 @@
         <v>21</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>264</v>
+        <v>201</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>21</v>
@@ -4577,42 +4374,46 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>265</v>
+        <v>242</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>265</v>
+        <v>242</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>21</v>
+        <v>206</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>164</v>
+        <v>207</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>21</v>
       </c>
@@ -4660,25 +4461,25 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>166</v>
+        <v>209</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>167</v>
+        <v>130</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>21</v>
@@ -4689,21 +4490,21 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>21</v>
@@ -4715,17 +4516,15 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>133</v>
+        <v>197</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>134</v>
+        <v>244</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -4774,75 +4573,71 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK30" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="AG30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK30" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AL30" t="s" s="2">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>21</v>
+        <v>246</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>268</v>
+        <v>21</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>133</v>
+        <v>248</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>269</v>
+        <v>249</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>21</v>
       </c>
@@ -4890,1283 +4685,35 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>271</v>
+        <v>247</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>130</v>
+        <v>251</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="32" hidden="true">
-      <c r="A32" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="C32" s="2"/>
-      <c r="D32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E32" s="2"/>
-      <c r="F32" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="G32" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K32" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="P32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q32" s="2"/>
-      <c r="R32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="AC32" s="2"/>
-      <c r="AD32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="D33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E33" s="2"/>
-      <c r="F33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G33" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H33" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="I33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K33" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="P33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q33" s="2"/>
-      <c r="R33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AG33" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK33" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="D34" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E34" s="2"/>
-      <c r="F34" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G34" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H34" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="I34" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J34" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K34" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="L34" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="P34" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q34" s="2"/>
-      <c r="R34" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S34" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T34" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U34" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V34" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W34" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X34" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AG34" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI34" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ34" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK34" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="C35" s="2"/>
-      <c r="D35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E35" s="2"/>
-      <c r="F35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G35" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H35" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="I35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K35" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="L35" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="P35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q35" s="2"/>
-      <c r="R35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="AG35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="C36" s="2"/>
-      <c r="D36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E36" s="2"/>
-      <c r="F36" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G36" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H36" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="I36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K36" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
-      <c r="P36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q36" s="2"/>
-      <c r="R36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AG36" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ36" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK36" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="37" hidden="true">
-      <c r="A37" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="C37" s="2"/>
-      <c r="D37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E37" s="2"/>
-      <c r="F37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K37" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
-      <c r="P37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q37" s="2"/>
-      <c r="R37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="AG37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="38" hidden="true">
-      <c r="A38" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="C38" s="2"/>
-      <c r="D38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E38" s="2"/>
-      <c r="F38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G38" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K38" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L38" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
-      <c r="P38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q38" s="2"/>
-      <c r="R38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="39" hidden="true">
-      <c r="A39" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="C39" s="2"/>
-      <c r="D39" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="E39" s="2"/>
-      <c r="F39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K39" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O39" s="2"/>
-      <c r="P39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q39" s="2"/>
-      <c r="R39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AG39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ39" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="40" hidden="true">
-      <c r="A40" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="C40" s="2"/>
-      <c r="D40" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="E40" s="2"/>
-      <c r="F40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H40" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I40" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="J40" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K40" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="P40" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q40" s="2"/>
-      <c r="R40" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S40" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T40" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U40" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V40" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W40" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X40" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="41" hidden="true">
-      <c r="A41" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="C41" s="2"/>
-      <c r="D41" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E41" s="2"/>
-      <c r="F41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G41" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H41" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I41" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J41" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K41" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
-      <c r="P41" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q41" s="2"/>
-      <c r="R41" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S41" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T41" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U41" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V41" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W41" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X41" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z41" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="AG41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI41" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ41" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK41" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="42" hidden="true">
-      <c r="A42" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="C42" s="2"/>
-      <c r="D42" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E42" s="2"/>
-      <c r="F42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G42" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H42" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I42" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J42" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K42" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
-      <c r="P42" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q42" s="2"/>
-      <c r="R42" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S42" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T42" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U42" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V42" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W42" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X42" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z42" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="AG42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI42" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK42" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>313</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN42">
+  <autoFilter ref="A1:AN31">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -6176,7 +4723,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI41">
+  <conditionalFormatting sqref="A2:AI30">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T10:11:27+00:00</t>
+    <t>2026-04-28T11:58:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-28T11:58:02+00:00</t>
+    <t>2026-04-29T14:27:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T14:27:58+00:00</t>
+    <t>2026-04-30T15:16:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T15:16:21+00:00</t>
+    <t>2026-04-30T15:23:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T15:23:35+00:00</t>
+    <t>2026-05-04T14:46:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-medication.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:46:25+00:00</t>
+    <t>2026-05-08T13:20:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
